--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D245"/>
+  <dimension ref="A1:D246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5812,6 +5812,28 @@
         </is>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>22 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>3818</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D246"/>
+  <dimension ref="A1:D247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5834,6 +5834,28 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>23 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>5721</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D247"/>
+  <dimension ref="A1:D248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5856,6 +5856,28 @@
         </is>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>24 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>8102</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D248"/>
+  <dimension ref="A1:D249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5878,6 +5878,28 @@
         </is>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>25 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>9179</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D249"/>
+  <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5900,6 +5900,28 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>26 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D250"/>
+  <dimension ref="A1:D251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5922,6 +5922,28 @@
         </is>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>29 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>6782</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D251"/>
+  <dimension ref="A1:D252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5944,6 +5944,28 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>30 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>8383</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D252"/>
+  <dimension ref="A1:D253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5966,6 +5966,28 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>1 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>8147</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D253"/>
+  <dimension ref="A1:D254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5988,6 +5988,28 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>9460</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D254"/>
+  <dimension ref="A1:D255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6010,6 +6010,28 @@
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>3 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>0392</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D255"/>
+  <dimension ref="A1:D256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6032,6 +6032,28 @@
         </is>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>6 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2227</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D256"/>
+  <dimension ref="A1:D257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6054,6 +6054,28 @@
         </is>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>7 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>9659</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D257"/>
+  <dimension ref="A1:D258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6076,6 +6076,28 @@
         </is>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>8 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>6920</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D258"/>
+  <dimension ref="A1:D259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6098,6 +6098,28 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>9 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D259"/>
+  <dimension ref="A1:D260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6120,6 +6120,28 @@
         </is>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>10 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D260"/>
+  <dimension ref="A1:D261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6142,6 +6142,28 @@
         </is>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>13 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D261"/>
+  <dimension ref="A1:D262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6164,6 +6164,28 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>14 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>1546</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D262"/>
+  <dimension ref="A1:D238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -513,320 +513,320 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10 ม.ค. 2568</t>
+          <t>13 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13 ม.ค. 2568</t>
+          <t>15 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15 ม.ค. 2568</t>
+          <t>17 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17 ม.ค. 2568</t>
+          <t>22 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20 ม.ค. 2568</t>
+          <t>24 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0086</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22 ม.ค. 2568</t>
+          <t>29 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>24 ม.ค. 2568</t>
+          <t>31 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>27 ม.ค. 2568</t>
+          <t>12 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>29 ม.ค. 2568</t>
+          <t>14 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>31 ม.ค. 2568</t>
+          <t>24 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3 ก.พ. 2568</t>
+          <t>24 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5 ก.พ. 2568</t>
+          <t>26 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7 ก.พ. 2568</t>
+          <t>31 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0055</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10 ก.พ. 2568</t>
+          <t>2 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>0609</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12 ก.พ. 2568</t>
+          <t>4 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -836,2439 +836,2439 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14 ก.พ. 2568</t>
+          <t>7 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17 ก.พ. 2568</t>
+          <t>9 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>19 ก.พ. 2568</t>
+          <t>18 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21 ก.พ. 2568</t>
+          <t>28 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>0702</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>24 ก.พ. 2568</t>
+          <t>30 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26 ก.พ. 2568</t>
+          <t>2 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>28 ก.พ. 2568</t>
+          <t>5 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3 มี.ค. 2568</t>
+          <t>7 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0411</t>
+          <t>0827</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5 มี.ค. 2568</t>
+          <t>9 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7 มี.ค. 2568</t>
+          <t>12 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>12 มี.ค. 2568</t>
+          <t>14 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14 มี.ค. 2568</t>
+          <t>16 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17 มี.ค. 2568</t>
+          <t>19 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>19 มี.ค. 2568</t>
+          <t>21 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>21 มี.ค. 2568</t>
+          <t>23 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>24 มี.ค. 2568</t>
+          <t>26 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>26 มี.ค. 2568</t>
+          <t>28 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>28 มี.ค. 2568</t>
+          <t>30 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>31 มี.ค. 2568</t>
+          <t>2 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2 เม.ย. 2568</t>
+          <t>4 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0609</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4 เม.ย. 2568</t>
+          <t>6 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7 เม.ย. 2568</t>
+          <t>9 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9 เม.ย. 2568</t>
+          <t>11 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>11 เม.ย. 2568</t>
+          <t>13 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>18 เม.ย. 2568</t>
+          <t>16 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21 เม.ย. 2568</t>
+          <t>18 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>23 เม.ย. 2568</t>
+          <t>20 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25 เม.ย. 2568</t>
+          <t>23 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28 เม.ย. 2568</t>
+          <t>25 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0702</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>30 เม.ย. 2568</t>
+          <t>27 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2 พ.ค. 2568</t>
+          <t>30 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5 พ.ค. 2568</t>
+          <t>2 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7 พ.ค. 2568</t>
+          <t>4 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0827</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9 พ.ค. 2568</t>
+          <t>7 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>12 พ.ค. 2568</t>
+          <t>9 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>14 พ.ค. 2568</t>
+          <t>11 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16 พ.ค. 2568</t>
+          <t>14 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19 พ.ค. 2568</t>
+          <t>16 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>21 พ.ค. 2568</t>
+          <t>18 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>23 พ.ค. 2568</t>
+          <t>21 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>26 พ.ค. 2568</t>
+          <t>23 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>0440</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>28 พ.ค. 2568</t>
+          <t>25 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>30 พ.ค. 2568</t>
+          <t>28 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2 มิ.ย. 2568</t>
+          <t>30 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4 มิ.ย. 2568</t>
+          <t>1 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6 มิ.ย. 2568</t>
+          <t>4 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>9 มิ.ย. 2568</t>
+          <t>6 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>11 มิ.ย. 2568</t>
+          <t>8 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>13 มิ.ย. 2568</t>
+          <t>11 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>16 มิ.ย. 2568</t>
+          <t>13 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>18 มิ.ย. 2568</t>
+          <t>15 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20 มิ.ย. 2568</t>
+          <t>18 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>23 มิ.ย. 2568</t>
+          <t>20 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>0722</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>25 มิ.ย. 2568</t>
+          <t>22 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>0568</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>27 มิ.ย. 2568</t>
+          <t>25 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>30 มิ.ย. 2568</t>
+          <t>27 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2 ก.ค. 2568</t>
+          <t>29 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4 ก.ค. 2568</t>
+          <t>1 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7 ก.ค. 2568</t>
+          <t>3 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>0701</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9 ก.ค. 2568</t>
+          <t>5 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11 ก.ค. 2568</t>
+          <t>8 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>14 ก.ค. 2568</t>
+          <t>10 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>16 ก.ค. 2568</t>
+          <t>12 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>0188</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>18 ก.ค. 2568</t>
+          <t>15 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>21 ก.ค. 2568</t>
+          <t>17 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>0543</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>23 ก.ค. 2568</t>
+          <t>19 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0440</t>
+          <t>0862</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>25 ก.ค. 2568</t>
+          <t>22 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>92</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>28 ก.ค. 2568</t>
+          <t>24 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>30 ก.ค. 2568</t>
+          <t>26 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1 ส.ค. 2568</t>
+          <t>29 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4 ส.ค. 2568</t>
+          <t>1 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6 ส.ค. 2568</t>
+          <t>3 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8 ส.ค. 2568</t>
+          <t>6 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>11 ส.ค. 2568</t>
+          <t>8 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>13 ส.ค. 2568</t>
+          <t>10 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>15 ส.ค. 2568</t>
+          <t>13 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>18 ส.ค. 2568</t>
+          <t>15 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20 ส.ค. 2568</t>
+          <t>17 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0722</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>22 ส.ค. 2568</t>
+          <t>20 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0568</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>25 ส.ค. 2568</t>
+          <t>22 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>27 ส.ค. 2568</t>
+          <t>24 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>29 ส.ค. 2568</t>
+          <t>27 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1 ก.ย. 2568</t>
+          <t>29 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3 ก.ย. 2568</t>
+          <t>31 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0701</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5 ก.ย. 2568</t>
+          <t>3 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8 ก.ย. 2568</t>
+          <t>5 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>10 ก.ย. 2568</t>
+          <t>7 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>12 ก.ย. 2568</t>
+          <t>10 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0188</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>15 ก.ย. 2568</t>
+          <t>12 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>17 ก.ย. 2568</t>
+          <t>14 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0543</t>
+          <t>9877</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>19 ก.ย. 2568</t>
+          <t>17 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0862</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>22 ก.ย. 2568</t>
+          <t>19 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>24 ก.ย. 2568</t>
+          <t>21 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>26 ก.ย. 2568</t>
+          <t>24 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>29 ก.ย. 2568</t>
+          <t>26 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1 ต.ค. 2568</t>
+          <t>28 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3 ต.ค. 2568</t>
+          <t>1 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>6 ต.ค. 2568</t>
+          <t>3 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>8 ต.ค. 2568</t>
+          <t>5 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10 ต.ค. 2568</t>
+          <t>8 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>13 ต.ค. 2568</t>
+          <t>10 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>15 ต.ค. 2568</t>
+          <t>12 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>17 ต.ค. 2568</t>
+          <t>15 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>20 ต.ค. 2568</t>
+          <t>17 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>22 ต.ค. 2568</t>
+          <t>19 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>24 ต.ค. 2568</t>
+          <t>22 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>27 ต.ค. 2568</t>
+          <t>24 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>29 ต.ค. 2568</t>
+          <t>26 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>0052</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
           <t>00</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>31 ต.ค. 2568</t>
+          <t>29 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3 พ.ย. 2568</t>
+          <t>31 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5 พ.ย. 2568</t>
+          <t>2 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3278,376 +3278,376 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>7 พ.ย. 2568</t>
+          <t>5 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10 พ.ย. 2568</t>
+          <t>7 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>12 พ.ย. 2568</t>
+          <t>9 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0905</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>14 พ.ย. 2568</t>
+          <t>12 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>17 พ.ย. 2568</t>
+          <t>14 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>19 พ.ย. 2568</t>
+          <t>16 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>21 พ.ย. 2568</t>
+          <t>19 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>24 พ.ย. 2568</t>
+          <t>21 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>26 พ.ย. 2568</t>
+          <t>23 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>28 พ.ย. 2568</t>
+          <t>26 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>0932</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1 ธ.ค. 2568</t>
+          <t>28 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3 ธ.ค. 2568</t>
+          <t>30 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5 ธ.ค. 2568</t>
+          <t>2 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8 ธ.ค. 2568</t>
+          <t>4 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>10 ธ.ค. 2568</t>
+          <t>6 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>12 ธ.ค. 2568</t>
+          <t>9 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>15 ธ.ค. 2568</t>
+          <t>11 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3659,105 +3659,105 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>17 ธ.ค. 2568</t>
+          <t>13 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>19 ธ.ค. 2568</t>
+          <t>16 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>22 ธ.ค. 2568</t>
+          <t>18 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>24 ธ.ค. 2568</t>
+          <t>20 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>26 ธ.ค. 2568</t>
+          <t>23 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0052</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3769,2420 +3769,1892 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>29 ธ.ค. 2568</t>
+          <t>25 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>31 ธ.ค. 2568</t>
+          <t>27 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2 ม.ค. 2569</t>
+          <t>2 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5 ม.ค. 2569</t>
+          <t>4 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>7 ม.ค. 2569</t>
+          <t>6 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>9 ม.ค. 2569</t>
+          <t>11 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0905</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>12 ม.ค. 2569</t>
+          <t>13 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>14 ม.ค. 2569</t>
+          <t>16 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>16 ม.ค. 2569</t>
+          <t>18 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>19 ม.ค. 2569</t>
+          <t>20 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>21 ม.ค. 2569</t>
+          <t>23 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>23 ม.ค. 2569</t>
+          <t>25 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>26 ม.ค. 2569</t>
+          <t>27 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0932</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>28 ม.ค. 2569</t>
+          <t>30 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>30 ม.ค. 2569</t>
+          <t>1 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2 ก.พ. 2569</t>
+          <t>2 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>0643</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4 ก.พ. 2569</t>
+          <t>3 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6 ก.พ. 2569</t>
+          <t>6 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>9 ก.พ. 2569</t>
+          <t>7 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>11 ก.พ. 2569</t>
+          <t>8 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>13 ก.พ. 2569</t>
+          <t>9 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>16 ก.พ. 2569</t>
+          <t>10 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>0389</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>18 ก.พ. 2569</t>
+          <t>13 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>20 ก.พ. 2569</t>
+          <t>17 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>23 ก.พ. 2569</t>
+          <t>20 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>0599</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>25 ก.พ. 2569</t>
+          <t>21 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>27 ก.พ. 2569</t>
+          <t>22 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2 มี.ค. 2569</t>
+          <t>23 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>4 มี.ค. 2569</t>
+          <t>24 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>6 มี.ค. 2569</t>
+          <t>27 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>0927</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>11 มี.ค. 2569</t>
+          <t>28 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>0947</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>13 มี.ค. 2569</t>
+          <t>29 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>16 มี.ค. 2569</t>
+          <t>30 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>18 มี.ค. 2569</t>
+          <t>4 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>20 มี.ค. 2569</t>
+          <t>5 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>23 มี.ค. 2569</t>
+          <t>6 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>25 มี.ค. 2569</t>
+          <t>7 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>27 มี.ค. 2569</t>
+          <t>8 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>30 มี.ค. 2569</t>
+          <t>11 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1 เม.ย. 2569</t>
+          <t>12 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2 เม.ย. 2569</t>
+          <t>13 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0643</t>
+          <t>0572</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3 เม.ย. 2569</t>
+          <t>14 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>6 เม.ย. 2569</t>
+          <t>15 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>7 เม.ย. 2569</t>
+          <t>18 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>8 เม.ย. 2569</t>
+          <t>19 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>9 เม.ย. 2569</t>
+          <t>20 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>10 เม.ย. 2569</t>
+          <t>21 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0389</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>13 เม.ย. 2569</t>
+          <t>22 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>17 เม.ย. 2569</t>
+          <t>25 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>20 เม.ย. 2569</t>
+          <t>26 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0599</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>21 เม.ย. 2569</t>
+          <t>27 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>22 เม.ย. 2569</t>
+          <t>28 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>23 เม.ย. 2569</t>
+          <t>29 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>24 เม.ย. 2569</t>
+          <t>1 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>27 เม.ย. 2569</t>
+          <t>2 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0927</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>28 เม.ย. 2569</t>
+          <t>3 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0947</t>
+          <t>0549</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>29 เม.ย. 2569</t>
+          <t>4 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>30 เม.ย. 2569</t>
+          <t>5 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4 พ.ค. 2569</t>
+          <t>8 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5 พ.ค. 2569</t>
+          <t>9 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>6 พ.ค. 2569</t>
+          <t>10 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>7 พ.ค. 2569</t>
+          <t>11 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>8 พ.ค. 2569</t>
+          <t>12 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>11 พ.ค. 2569</t>
+          <t>15 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>12 พ.ค. 2569</t>
+          <t>16 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>13 พ.ค. 2569</t>
+          <t>17 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>0572</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>14 พ.ค. 2569</t>
+          <t>18 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>15 พ.ค. 2569</t>
+          <t>19 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>18 พ.ค. 2569</t>
+          <t>22 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>19 พ.ค. 2569</t>
+          <t>23 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>20 พ.ค. 2569</t>
+          <t>24 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>21 พ.ค. 2569</t>
+          <t>25 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>22 พ.ค. 2569</t>
+          <t>26 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>25 พ.ค. 2569</t>
+          <t>29 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>26 พ.ค. 2569</t>
+          <t>30 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>83</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>27 พ.ค. 2569</t>
+          <t>1 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>28 พ.ค. 2569</t>
+          <t>2 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>29 พ.ค. 2569</t>
+          <t>3 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1 มิ.ย. 2569</t>
+          <t>6 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2 มิ.ย. 2569</t>
+          <t>7 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3 มิ.ย. 2569</t>
+          <t>8 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0549</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>4 มิ.ย. 2569</t>
+          <t>9 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5 มิ.ย. 2569</t>
+          <t>10 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>8 มิ.ย. 2569</t>
+          <t>13 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>9 มิ.ย. 2569</t>
+          <t>14 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>10 มิ.ย. 2569</t>
+          <t>15 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>11 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>5411</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>12 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>5060</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>15 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>16 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>5883</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>17 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>18 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>3430</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>19 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>4240</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>22 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>3818</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>23 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>5721</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>24 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>8102</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>25 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>9179</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>26 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>1577</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>29 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>6782</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>30 มิ.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>8383</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>1 ก.ค. 2569</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>2 ก.ค. 2569</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>9460</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>3 ก.ค. 2569</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>0392</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>6 ก.ค. 2569</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>2227</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>7 ก.ค. 2569</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>9659</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>8 ก.ค. 2569</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>6920</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>9 ก.ค. 2569</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>10 ก.ค. 2569</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>0277</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>13 ก.ค. 2569</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>2866</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>14 ก.ค. 2569</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>93</t>
         </is>
       </c>
     </row>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D238"/>
+  <dimension ref="A1:D264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -513,320 +513,320 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13 ม.ค. 2568</t>
+          <t>10 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15 ม.ค. 2568</t>
+          <t>13 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17 ม.ค. 2568</t>
+          <t>15 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22 ม.ค. 2568</t>
+          <t>17 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24 ม.ค. 2568</t>
+          <t>20 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>0086</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29 ม.ค. 2568</t>
+          <t>22 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>31 ม.ค. 2568</t>
+          <t>24 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12 ก.พ. 2568</t>
+          <t>27 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14 ก.พ. 2568</t>
+          <t>29 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24 ก.พ. 2568</t>
+          <t>31 ม.ค. 2568</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24 มี.ค. 2568</t>
+          <t>3 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26 มี.ค. 2568</t>
+          <t>5 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>31 มี.ค. 2568</t>
+          <t>7 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>0055</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2 เม.ย. 2568</t>
+          <t>10 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0609</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4 เม.ย. 2568</t>
+          <t>12 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -836,2439 +836,2439 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7 เม.ย. 2568</t>
+          <t>14 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9 เม.ย. 2568</t>
+          <t>17 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18 เม.ย. 2568</t>
+          <t>19 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>28 เม.ย. 2568</t>
+          <t>21 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0702</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>30 เม.ย. 2568</t>
+          <t>24 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2 พ.ค. 2568</t>
+          <t>26 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5 พ.ค. 2568</t>
+          <t>28 ก.พ. 2568</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7 พ.ค. 2568</t>
+          <t>3 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0827</t>
+          <t>0411</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9 พ.ค. 2568</t>
+          <t>5 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>12 พ.ค. 2568</t>
+          <t>7 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14 พ.ค. 2568</t>
+          <t>12 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>16 พ.ค. 2568</t>
+          <t>14 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>19 พ.ค. 2568</t>
+          <t>17 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>21 พ.ค. 2568</t>
+          <t>19 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>23 พ.ค. 2568</t>
+          <t>21 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>26 พ.ค. 2568</t>
+          <t>24 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>28 พ.ค. 2568</t>
+          <t>26 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>30 พ.ค. 2568</t>
+          <t>28 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2 มิ.ย. 2568</t>
+          <t>31 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4 มิ.ย. 2568</t>
+          <t>2 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>0609</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6 มิ.ย. 2568</t>
+          <t>4 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9 มิ.ย. 2568</t>
+          <t>7 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>11 มิ.ย. 2568</t>
+          <t>9 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13 มิ.ย. 2568</t>
+          <t>11 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>16 มิ.ย. 2568</t>
+          <t>18 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>18 มิ.ย. 2568</t>
+          <t>21 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20 มิ.ย. 2568</t>
+          <t>23 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>23 มิ.ย. 2568</t>
+          <t>25 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>25 มิ.ย. 2568</t>
+          <t>28 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>0702</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>27 มิ.ย. 2568</t>
+          <t>30 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>30 มิ.ย. 2568</t>
+          <t>2 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2 ก.ค. 2568</t>
+          <t>5 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4 ก.ค. 2568</t>
+          <t>7 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>0827</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7 ก.ค. 2568</t>
+          <t>9 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>9 ก.ค. 2568</t>
+          <t>12 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>11 ก.ค. 2568</t>
+          <t>14 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>14 ก.ค. 2568</t>
+          <t>16 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16 ก.ค. 2568</t>
+          <t>19 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>18 ก.ค. 2568</t>
+          <t>21 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21 ก.ค. 2568</t>
+          <t>23 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>23 ก.ค. 2568</t>
+          <t>26 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0440</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>25 ก.ค. 2568</t>
+          <t>28 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>28 ก.ค. 2568</t>
+          <t>30 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>30 ก.ค. 2568</t>
+          <t>2 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1 ส.ค. 2568</t>
+          <t>4 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4 ส.ค. 2568</t>
+          <t>6 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6 ส.ค. 2568</t>
+          <t>9 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8 ส.ค. 2568</t>
+          <t>11 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11 ส.ค. 2568</t>
+          <t>13 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>13 ส.ค. 2568</t>
+          <t>16 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>15 ส.ค. 2568</t>
+          <t>18 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>18 ส.ค. 2568</t>
+          <t>20 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20 ส.ค. 2568</t>
+          <t>23 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0722</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>22 ส.ค. 2568</t>
+          <t>25 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0568</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>25 ส.ค. 2568</t>
+          <t>27 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>27 ส.ค. 2568</t>
+          <t>30 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>29 ส.ค. 2568</t>
+          <t>2 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1 ก.ย. 2568</t>
+          <t>4 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3 ก.ย. 2568</t>
+          <t>7 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0701</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5 ก.ย. 2568</t>
+          <t>9 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8 ก.ย. 2568</t>
+          <t>11 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10 ก.ย. 2568</t>
+          <t>14 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>12 ก.ย. 2568</t>
+          <t>16 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0188</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>15 ก.ย. 2568</t>
+          <t>18 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>17 ก.ย. 2568</t>
+          <t>21 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0543</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>19 ก.ย. 2568</t>
+          <t>23 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0862</t>
+          <t>0440</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>22 ก.ย. 2568</t>
+          <t>25 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>24 ก.ย. 2568</t>
+          <t>28 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>26 ก.ย. 2568</t>
+          <t>30 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>29 ก.ย. 2568</t>
+          <t>1 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1 ต.ค. 2568</t>
+          <t>4 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3 ต.ค. 2568</t>
+          <t>6 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6 ต.ค. 2568</t>
+          <t>8 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8 ต.ค. 2568</t>
+          <t>11 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10 ต.ค. 2568</t>
+          <t>13 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>13 ต.ค. 2568</t>
+          <t>15 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>15 ต.ค. 2568</t>
+          <t>18 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>17 ต.ค. 2568</t>
+          <t>20 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>0722</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20 ต.ค. 2568</t>
+          <t>22 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>0568</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>22 ต.ค. 2568</t>
+          <t>25 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>24 ต.ค. 2568</t>
+          <t>27 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>27 ต.ค. 2568</t>
+          <t>29 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>29 ต.ค. 2568</t>
+          <t>1 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>31 ต.ค. 2568</t>
+          <t>3 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>0701</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3 พ.ย. 2568</t>
+          <t>5 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5 พ.ย. 2568</t>
+          <t>8 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7 พ.ย. 2568</t>
+          <t>10 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>10 พ.ย. 2568</t>
+          <t>12 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>0188</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>12 พ.ย. 2568</t>
+          <t>15 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>14 พ.ย. 2568</t>
+          <t>17 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>0543</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>17 พ.ย. 2568</t>
+          <t>19 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>0862</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>19 พ.ย. 2568</t>
+          <t>22 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>92</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>21 พ.ย. 2568</t>
+          <t>24 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>24 พ.ย. 2568</t>
+          <t>26 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>26 พ.ย. 2568</t>
+          <t>29 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>28 พ.ย. 2568</t>
+          <t>1 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1 ธ.ค. 2568</t>
+          <t>3 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3 ธ.ค. 2568</t>
+          <t>6 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5 ธ.ค. 2568</t>
+          <t>8 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8 ธ.ค. 2568</t>
+          <t>10 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>10 ธ.ค. 2568</t>
+          <t>13 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>12 ธ.ค. 2568</t>
+          <t>15 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>15 ธ.ค. 2568</t>
+          <t>17 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>17 ธ.ค. 2568</t>
+          <t>20 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>19 ธ.ค. 2568</t>
+          <t>22 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>22 ธ.ค. 2568</t>
+          <t>24 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>24 ธ.ค. 2568</t>
+          <t>27 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>26 ธ.ค. 2568</t>
+          <t>29 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0052</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>29 ธ.ค. 2568</t>
+          <t>31 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>31 ธ.ค. 2568</t>
+          <t>3 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2 ม.ค. 2569</t>
+          <t>5 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3278,376 +3278,376 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5 ม.ค. 2569</t>
+          <t>7 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>7 ม.ค. 2569</t>
+          <t>10 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>9 ม.ค. 2569</t>
+          <t>12 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0905</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>12 ม.ค. 2569</t>
+          <t>14 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>9877</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>14 ม.ค. 2569</t>
+          <t>17 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>16 ม.ค. 2569</t>
+          <t>19 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>19 ม.ค. 2569</t>
+          <t>21 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>21 ม.ค. 2569</t>
+          <t>24 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>23 ม.ค. 2569</t>
+          <t>26 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>26 ม.ค. 2569</t>
+          <t>28 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0932</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>28 ม.ค. 2569</t>
+          <t>1 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>30 ม.ค. 2569</t>
+          <t>3 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2 ก.พ. 2569</t>
+          <t>5 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4 ก.พ. 2569</t>
+          <t>8 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6 ก.พ. 2569</t>
+          <t>10 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>9 ก.พ. 2569</t>
+          <t>12 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>11 ก.พ. 2569</t>
+          <t>15 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3659,105 +3659,105 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>13 ก.พ. 2569</t>
+          <t>17 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>16 ก.พ. 2569</t>
+          <t>19 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>18 ก.พ. 2569</t>
+          <t>22 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>20 ก.พ. 2569</t>
+          <t>24 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>23 ก.พ. 2569</t>
+          <t>26 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>0052</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3769,1892 +3769,2464 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>25 ก.พ. 2569</t>
+          <t>29 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>27 ก.พ. 2569</t>
+          <t>31 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2 มี.ค. 2569</t>
+          <t>2 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4 มี.ค. 2569</t>
+          <t>5 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>6 มี.ค. 2569</t>
+          <t>7 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>11 มี.ค. 2569</t>
+          <t>9 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>0905</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>13 มี.ค. 2569</t>
+          <t>12 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>16 มี.ค. 2569</t>
+          <t>14 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>18 มี.ค. 2569</t>
+          <t>16 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>20 มี.ค. 2569</t>
+          <t>19 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>23 มี.ค. 2569</t>
+          <t>21 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>25 มี.ค. 2569</t>
+          <t>23 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>27 มี.ค. 2569</t>
+          <t>26 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>0932</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>30 มี.ค. 2569</t>
+          <t>28 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1 เม.ย. 2569</t>
+          <t>30 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2 เม.ย. 2569</t>
+          <t>2 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0643</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3 เม.ย. 2569</t>
+          <t>4 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6 เม.ย. 2569</t>
+          <t>6 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>7 เม.ย. 2569</t>
+          <t>9 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>8 เม.ย. 2569</t>
+          <t>11 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>9 เม.ย. 2569</t>
+          <t>13 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>10 เม.ย. 2569</t>
+          <t>16 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0389</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>13 เม.ย. 2569</t>
+          <t>18 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>17 เม.ย. 2569</t>
+          <t>20 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>20 เม.ย. 2569</t>
+          <t>23 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0599</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>21 เม.ย. 2569</t>
+          <t>25 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>22 เม.ย. 2569</t>
+          <t>27 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>23 เม.ย. 2569</t>
+          <t>2 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>24 เม.ย. 2569</t>
+          <t>4 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>27 เม.ย. 2569</t>
+          <t>6 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0927</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>28 เม.ย. 2569</t>
+          <t>11 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0947</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>29 เม.ย. 2569</t>
+          <t>13 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>30 เม.ย. 2569</t>
+          <t>16 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>4 พ.ค. 2569</t>
+          <t>18 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5 พ.ค. 2569</t>
+          <t>20 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>6 พ.ค. 2569</t>
+          <t>23 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>7 พ.ค. 2569</t>
+          <t>25 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>8 พ.ค. 2569</t>
+          <t>27 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>11 พ.ค. 2569</t>
+          <t>30 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>12 พ.ค. 2569</t>
+          <t>1 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>13 พ.ค. 2569</t>
+          <t>2 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0572</t>
+          <t>0643</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>14 พ.ค. 2569</t>
+          <t>3 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>15 พ.ค. 2569</t>
+          <t>6 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>18 พ.ค. 2569</t>
+          <t>7 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>19 พ.ค. 2569</t>
+          <t>8 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>20 พ.ค. 2569</t>
+          <t>9 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>21 พ.ค. 2569</t>
+          <t>10 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>0389</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>22 พ.ค. 2569</t>
+          <t>13 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>25 พ.ค. 2569</t>
+          <t>17 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>26 พ.ค. 2569</t>
+          <t>20 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>0599</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>27 พ.ค. 2569</t>
+          <t>21 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>28 พ.ค. 2569</t>
+          <t>22 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>29 พ.ค. 2569</t>
+          <t>23 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1 มิ.ย. 2569</t>
+          <t>24 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2 มิ.ย. 2569</t>
+          <t>27 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>0927</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>3 มิ.ย. 2569</t>
+          <t>28 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0549</t>
+          <t>0947</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4 มิ.ย. 2569</t>
+          <t>29 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5 มิ.ย. 2569</t>
+          <t>30 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>8 มิ.ย. 2569</t>
+          <t>4 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>9 มิ.ย. 2569</t>
+          <t>5 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>10 มิ.ย. 2569</t>
+          <t>6 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>11 มิ.ย. 2569</t>
+          <t>7 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>12 มิ.ย. 2569</t>
+          <t>8 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>15 มิ.ย. 2569</t>
+          <t>11 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>16 มิ.ย. 2569</t>
+          <t>12 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>17 มิ.ย. 2569</t>
+          <t>13 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>0572</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>18 มิ.ย. 2569</t>
+          <t>14 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>19 มิ.ย. 2569</t>
+          <t>15 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>22 มิ.ย. 2569</t>
+          <t>18 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>23 มิ.ย. 2569</t>
+          <t>19 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>24 มิ.ย. 2569</t>
+          <t>20 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>25 มิ.ย. 2569</t>
+          <t>21 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>26 มิ.ย. 2569</t>
+          <t>22 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>29 มิ.ย. 2569</t>
+          <t>25 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>30 มิ.ย. 2569</t>
+          <t>26 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1 ก.ค. 2569</t>
+          <t>27 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2 ก.ค. 2569</t>
+          <t>28 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>3 ก.ค. 2569</t>
+          <t>29 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>6 ก.ค. 2569</t>
+          <t>1 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>7 ก.ค. 2569</t>
+          <t>2 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>8 ก.ค. 2569</t>
+          <t>3 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>0549</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>9 ก.ค. 2569</t>
+          <t>4 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>10 ก.ค. 2569</t>
+          <t>5 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>13 ก.ค. 2569</t>
+          <t>8 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>14 ก.ค. 2569</t>
+          <t>9 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
+          <t>10 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>4557</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>11 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>5411</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>12 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>5060</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>15 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>16 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>5883</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>17 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>18 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>19 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>4240</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>22 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>3818</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>23 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>5721</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>24 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>8102</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>25 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>9179</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>26 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>29 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>6782</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>30 มิ.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>8383</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>1 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>8147</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>9460</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>3 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>0392</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>6 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2227</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>7 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>9659</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>8 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>6920</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>9 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>10 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>13 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>14 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>1546</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
           <t>15 ก.ค. 2569</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>9375</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="C263" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D263" t="inlineStr">
         <is>
           <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>16 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>6395</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>63</t>
         </is>
       </c>
     </row>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D264"/>
+  <dimension ref="A1:D265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6230,6 +6230,28 @@
         </is>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>17 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>4604</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D265"/>
+  <dimension ref="A1:D266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6252,6 +6252,28 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>20 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>9073</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D266"/>
+  <dimension ref="A1:D267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6274,6 +6274,28 @@
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>21 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>6592</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D267"/>
+  <dimension ref="A1:D268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6296,6 +6296,28 @@
         </is>
       </c>
     </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>22 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>0768</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D268"/>
+  <dimension ref="A1:D269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6318,6 +6318,28 @@
         </is>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>23 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>6276</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D269"/>
+  <dimension ref="A1:D270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6340,6 +6340,28 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>24 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2561</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D270"/>
+  <dimension ref="A1:D271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6362,6 +6362,28 @@
         </is>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>27 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>4970</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D271"/>
+  <dimension ref="A1:D272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6384,6 +6384,28 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>28 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>0480</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D272"/>
+  <dimension ref="A1:D273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6406,6 +6406,28 @@
         </is>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>29 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D273"/>
+  <dimension ref="A1:D274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6428,6 +6428,28 @@
         </is>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>30 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>0702</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D274"/>
+  <dimension ref="A1:D275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6450,6 +6450,28 @@
         </is>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>31 ก.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>3290</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D275"/>
+  <dimension ref="A1:D276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6472,6 +6472,28 @@
         </is>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>3 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>1680</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D276"/>
+  <dimension ref="A1:D277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6494,6 +6494,28 @@
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>4 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>7886</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D277"/>
+  <dimension ref="A1:D278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6516,6 +6516,28 @@
         </is>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>5 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2222</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D278"/>
+  <dimension ref="A1:D280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6538,6 +6538,50 @@
         </is>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>6 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>7634</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>7 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>7677</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D280"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6582,6 +6582,28 @@
         </is>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>10 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D281"/>
+  <dimension ref="A1:D282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6604,6 +6604,28 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>11 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>9670</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D282"/>
+  <dimension ref="A1:D283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6626,6 +6626,28 @@
         </is>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>12 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>9718</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D283"/>
+  <dimension ref="A1:D284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6648,6 +6648,28 @@
         </is>
       </c>
     </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>13 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>3606</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D284"/>
+  <dimension ref="A1:D285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6670,6 +6670,28 @@
         </is>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>14 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>7941</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D285"/>
+  <dimension ref="A1:D286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6692,6 +6692,28 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>17 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>6707</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D286"/>
+  <dimension ref="A1:D287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6714,6 +6714,28 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>18 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>8222</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D287"/>
+  <dimension ref="A1:D288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6736,6 +6736,28 @@
         </is>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>19 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>6063</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D288"/>
+  <dimension ref="A1:D289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6758,6 +6758,28 @@
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>20 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D289"/>
+  <dimension ref="A1:D290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6780,6 +6780,28 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>21 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>0253</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D290"/>
+  <dimension ref="A1:D288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4891,672 +4891,672 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>22 เม.ย. 2569</t>
+          <t>23 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>23 เม.ย. 2569</t>
+          <t>27 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>0927</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>24 เม.ย. 2569</t>
+          <t>28 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>0947</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>27 เม.ย. 2569</t>
+          <t>29 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0927</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>28 เม.ย. 2569</t>
+          <t>30 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0947</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>29 เม.ย. 2569</t>
+          <t>4 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>30 เม.ย. 2569</t>
+          <t>5 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4 พ.ค. 2569</t>
+          <t>6 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5 พ.ค. 2569</t>
+          <t>7 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>6 พ.ค. 2569</t>
+          <t>8 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>7 พ.ค. 2569</t>
+          <t>11 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>8 พ.ค. 2569</t>
+          <t>12 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>11 พ.ค. 2569</t>
+          <t>13 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>0572</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>12 พ.ค. 2569</t>
+          <t>14 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>13 พ.ค. 2569</t>
+          <t>15 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>0572</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>14 พ.ค. 2569</t>
+          <t>18 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>15 พ.ค. 2569</t>
+          <t>19 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>18 พ.ค. 2569</t>
+          <t>20 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>19 พ.ค. 2569</t>
+          <t>21 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>20 พ.ค. 2569</t>
+          <t>22 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>21 พ.ค. 2569</t>
+          <t>25 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>22 พ.ค. 2569</t>
+          <t>26 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>25 พ.ค. 2569</t>
+          <t>27 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>26 พ.ค. 2569</t>
+          <t>28 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>27 พ.ค. 2569</t>
+          <t>29 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>28 พ.ค. 2569</t>
+          <t>1 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>29 พ.ค. 2569</t>
+          <t>2 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1 มิ.ย. 2569</t>
+          <t>3 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>0549</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2 มิ.ย. 2569</t>
+          <t>4 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3 มิ.ย. 2569</t>
+          <t>5 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0549</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>4 มิ.ย. 2569</t>
+          <t>8 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5566,552 +5566,552 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5 มิ.ย. 2569</t>
+          <t>9 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>8 มิ.ย. 2569</t>
+          <t>10 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>9 มิ.ย. 2569</t>
+          <t>11 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>10 มิ.ย. 2569</t>
+          <t>12 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>11 มิ.ย. 2569</t>
+          <t>15 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>12 มิ.ย. 2569</t>
+          <t>16 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>15 มิ.ย. 2569</t>
+          <t>17 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>16 มิ.ย. 2569</t>
+          <t>18 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>17 มิ.ย. 2569</t>
+          <t>19 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>18 มิ.ย. 2569</t>
+          <t>22 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>19 มิ.ย. 2569</t>
+          <t>23 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>22 มิ.ย. 2569</t>
+          <t>24 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>23 มิ.ย. 2569</t>
+          <t>25 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>24 มิ.ย. 2569</t>
+          <t>26 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>25 มิ.ย. 2569</t>
+          <t>29 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>26 มิ.ย. 2569</t>
+          <t>30 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>83</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>29 มิ.ย. 2569</t>
+          <t>1 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>30 มิ.ย. 2569</t>
+          <t>2 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1 ก.ค. 2569</t>
+          <t>3 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2 ก.ค. 2569</t>
+          <t>6 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3 ก.ค. 2569</t>
+          <t>7 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>6 ก.ค. 2569</t>
+          <t>8 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>7 ก.ค. 2569</t>
+          <t>9 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>8 ก.ค. 2569</t>
+          <t>10 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>9 ก.ค. 2569</t>
+          <t>13 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6123,680 +6123,636 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>10 ก.ค. 2569</t>
+          <t>14 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>13 ก.ค. 2569</t>
+          <t>15 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>93</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>14 ก.ค. 2569</t>
+          <t>16 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>15 ก.ค. 2569</t>
+          <t>17 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>16 ก.ค. 2569</t>
+          <t>20 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>17 ก.ค. 2569</t>
+          <t>21 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>20 ก.ค. 2569</t>
+          <t>22 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>0768</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>21 ก.ค. 2569</t>
+          <t>23 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>22 ก.ค. 2569</t>
+          <t>24 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>0768</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>23 ก.ค. 2569</t>
+          <t>27 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>24 ก.ค. 2569</t>
+          <t>28 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>0480</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>27 ก.ค. 2569</t>
+          <t>29 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>28 ก.ค. 2569</t>
+          <t>30 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>0480</t>
+          <t>0702</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>29 ก.ค. 2569</t>
+          <t>31 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>30 ก.ค. 2569</t>
+          <t>3 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>0702</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>31 ก.ค. 2569</t>
+          <t>4 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>3 ส.ค. 2569</t>
+          <t>5 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>4 ส.ค. 2569</t>
+          <t>6 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5 ส.ค. 2569</t>
+          <t>7 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>6 ส.ค. 2569</t>
+          <t>10 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>7 ส.ค. 2569</t>
+          <t>11 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>10 ส.ค. 2569</t>
+          <t>12 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>11 ส.ค. 2569</t>
+          <t>13 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>12 ส.ค. 2569</t>
+          <t>14 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>13 ส.ค. 2569</t>
+          <t>17 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>14 ส.ค. 2569</t>
+          <t>18 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>17 ส.ค. 2569</t>
+          <t>19 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>18 ส.ค. 2569</t>
+          <t>20 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>19 ส.ค. 2569</t>
+          <t>21 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>0253</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>20 ส.ค. 2569</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>4900</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>21 ส.ค. 2569</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>0253</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
         <is>
           <t>02</t>
         </is>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D288"/>
+  <dimension ref="A1:D292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4891,672 +4891,672 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>23 เม.ย. 2569</t>
+          <t>22 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>27 เม.ย. 2569</t>
+          <t>23 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>0927</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>28 เม.ย. 2569</t>
+          <t>24 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>0947</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>29 เม.ย. 2569</t>
+          <t>27 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>0927</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>30 เม.ย. 2569</t>
+          <t>28 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0947</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4 พ.ค. 2569</t>
+          <t>29 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5 พ.ค. 2569</t>
+          <t>30 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>6 พ.ค. 2569</t>
+          <t>4 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>7 พ.ค. 2569</t>
+          <t>5 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>8 พ.ค. 2569</t>
+          <t>6 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>11 พ.ค. 2569</t>
+          <t>7 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>12 พ.ค. 2569</t>
+          <t>8 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>13 พ.ค. 2569</t>
+          <t>11 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>0572</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>14 พ.ค. 2569</t>
+          <t>12 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>15 พ.ค. 2569</t>
+          <t>13 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>0572</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>18 พ.ค. 2569</t>
+          <t>14 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>19 พ.ค. 2569</t>
+          <t>15 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
           <t>70</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>04</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>20 พ.ค. 2569</t>
+          <t>18 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>21 พ.ค. 2569</t>
+          <t>19 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>22 พ.ค. 2569</t>
+          <t>20 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>25 พ.ค. 2569</t>
+          <t>21 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>26 พ.ค. 2569</t>
+          <t>22 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>27 พ.ค. 2569</t>
+          <t>25 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>28 พ.ค. 2569</t>
+          <t>26 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>29 พ.ค. 2569</t>
+          <t>27 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1 มิ.ย. 2569</t>
+          <t>28 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2 มิ.ย. 2569</t>
+          <t>29 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>3 มิ.ย. 2569</t>
+          <t>1 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>0549</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>4 มิ.ย. 2569</t>
+          <t>2 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>5 มิ.ย. 2569</t>
+          <t>3 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>0549</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>8 มิ.ย. 2569</t>
+          <t>4 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5566,552 +5566,552 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>9 มิ.ย. 2569</t>
+          <t>5 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>10 มิ.ย. 2569</t>
+          <t>8 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>11 มิ.ย. 2569</t>
+          <t>9 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>12 มิ.ย. 2569</t>
+          <t>10 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>15 มิ.ย. 2569</t>
+          <t>11 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>16 มิ.ย. 2569</t>
+          <t>12 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>17 มิ.ย. 2569</t>
+          <t>15 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>18 มิ.ย. 2569</t>
+          <t>16 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>19 มิ.ย. 2569</t>
+          <t>17 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>22 มิ.ย. 2569</t>
+          <t>18 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>23 มิ.ย. 2569</t>
+          <t>19 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>24 มิ.ย. 2569</t>
+          <t>22 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>25 มิ.ย. 2569</t>
+          <t>23 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>26 มิ.ย. 2569</t>
+          <t>24 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>29 มิ.ย. 2569</t>
+          <t>25 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>30 มิ.ย. 2569</t>
+          <t>26 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1 ก.ค. 2569</t>
+          <t>29 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2 ก.ค. 2569</t>
+          <t>30 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>83</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3 ก.ค. 2569</t>
+          <t>1 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>6 ก.ค. 2569</t>
+          <t>2 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>7 ก.ค. 2569</t>
+          <t>3 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>8 ก.ค. 2569</t>
+          <t>6 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>9 ก.ค. 2569</t>
+          <t>7 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>10 ก.ค. 2569</t>
+          <t>8 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>13 ก.ค. 2569</t>
+          <t>9 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6123,638 +6123,726 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>14 ก.ค. 2569</t>
+          <t>10 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>15 ก.ค. 2569</t>
+          <t>13 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>16 ก.ค. 2569</t>
+          <t>14 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>17 ก.ค. 2569</t>
+          <t>15 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>93</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>20 ก.ค. 2569</t>
+          <t>16 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>21 ก.ค. 2569</t>
+          <t>17 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>22 ก.ค. 2569</t>
+          <t>20 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>0768</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>23 ก.ค. 2569</t>
+          <t>21 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>24 ก.ค. 2569</t>
+          <t>22 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>0768</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>27 ก.ค. 2569</t>
+          <t>23 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>28 ก.ค. 2569</t>
+          <t>24 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>0480</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>29 ก.ค. 2569</t>
+          <t>27 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>30 ก.ค. 2569</t>
+          <t>28 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>0702</t>
+          <t>0480</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>31 ก.ค. 2569</t>
+          <t>29 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>3 ส.ค. 2569</t>
+          <t>30 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>0702</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>4 ส.ค. 2569</t>
+          <t>31 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5 ส.ค. 2569</t>
+          <t>3 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>6 ส.ค. 2569</t>
+          <t>4 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>7 ส.ค. 2569</t>
+          <t>5 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>10 ส.ค. 2569</t>
+          <t>6 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>11 ส.ค. 2569</t>
+          <t>7 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>12 ส.ค. 2569</t>
+          <t>10 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>13 ส.ค. 2569</t>
+          <t>11 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>14 ส.ค. 2569</t>
+          <t>12 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>17 ส.ค. 2569</t>
+          <t>13 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>18 ส.ค. 2569</t>
+          <t>14 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>19 ส.ค. 2569</t>
+          <t>17 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>20 ส.ค. 2569</t>
+          <t>18 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
+          <t>19 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>6063</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>20 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
           <t>21 ส.ค. 2569</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
+      <c r="B290" t="inlineStr">
         <is>
           <t>0253</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
+      <c r="C290" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
+      <c r="D290" t="inlineStr">
         <is>
           <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>24 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>5552</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>25 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>6600</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>66</t>
         </is>
       </c>
     </row>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D292"/>
+  <dimension ref="A1:D293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6846,6 +6846,28 @@
         </is>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>26 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>5523</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D293"/>
+  <dimension ref="A1:D294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6868,6 +6868,28 @@
         </is>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>27 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>9759</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D294"/>
+  <dimension ref="A1:D295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6890,6 +6890,28 @@
         </is>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>28 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>0623</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D295"/>
+  <dimension ref="A1:D296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6912,6 +6912,28 @@
         </is>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>31 ส.ค. 2569</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>4389</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D296"/>
+  <dimension ref="A1:D297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6934,6 +6934,28 @@
         </is>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>1 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>8475</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D297"/>
+  <dimension ref="A1:D299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6956,6 +6956,50 @@
         </is>
       </c>
     </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>3 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D299"/>
+  <dimension ref="A1:D300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7000,6 +7000,28 @@
         </is>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>4 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>4187</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D300"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7022,6 +7022,28 @@
         </is>
       </c>
     </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>7 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D301"/>
+  <dimension ref="A1:D302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7044,6 +7044,28 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>8 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>3743</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D302"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5221,1178 +5221,1178 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>14 พ.ค. 2569</t>
+          <t>15 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>15 พ.ค. 2569</t>
+          <t>18 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>18 พ.ค. 2569</t>
+          <t>19 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>19 พ.ค. 2569</t>
+          <t>20 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>20 พ.ค. 2569</t>
+          <t>21 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>21 พ.ค. 2569</t>
+          <t>22 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>22 พ.ค. 2569</t>
+          <t>25 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>25 พ.ค. 2569</t>
+          <t>26 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>26 พ.ค. 2569</t>
+          <t>27 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>27 พ.ค. 2569</t>
+          <t>28 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>28 พ.ค. 2569</t>
+          <t>29 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>29 พ.ค. 2569</t>
+          <t>1 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1 มิ.ย. 2569</t>
+          <t>2 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2 มิ.ย. 2569</t>
+          <t>3 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>0549</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3 มิ.ย. 2569</t>
+          <t>4 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0549</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>4 มิ.ย. 2569</t>
+          <t>5 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5 มิ.ย. 2569</t>
+          <t>8 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>8 มิ.ย. 2569</t>
+          <t>9 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>9 มิ.ย. 2569</t>
+          <t>10 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>10 มิ.ย. 2569</t>
+          <t>11 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>11 มิ.ย. 2569</t>
+          <t>12 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>12 มิ.ย. 2569</t>
+          <t>15 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>15 มิ.ย. 2569</t>
+          <t>16 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>16 มิ.ย. 2569</t>
+          <t>17 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>17 มิ.ย. 2569</t>
+          <t>18 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>18 มิ.ย. 2569</t>
+          <t>19 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>19 มิ.ย. 2569</t>
+          <t>22 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>22 มิ.ย. 2569</t>
+          <t>23 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>23 มิ.ย. 2569</t>
+          <t>24 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>24 มิ.ย. 2569</t>
+          <t>25 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>25 มิ.ย. 2569</t>
+          <t>26 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>26 มิ.ย. 2569</t>
+          <t>29 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>29 มิ.ย. 2569</t>
+          <t>30 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>83</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>30 มิ.ย. 2569</t>
+          <t>1 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1 ก.ค. 2569</t>
+          <t>2 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2 ก.ค. 2569</t>
+          <t>3 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3 ก.ค. 2569</t>
+          <t>6 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>6 ก.ค. 2569</t>
+          <t>7 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>7 ก.ค. 2569</t>
+          <t>8 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>8 ก.ค. 2569</t>
+          <t>9 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>9 ก.ค. 2569</t>
+          <t>10 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>10 ก.ค. 2569</t>
+          <t>13 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>13 ก.ค. 2569</t>
+          <t>14 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>14 ก.ค. 2569</t>
+          <t>15 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>93</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>15 ก.ค. 2569</t>
+          <t>16 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>16 ก.ค. 2569</t>
+          <t>17 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>17 ก.ค. 2569</t>
+          <t>20 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>20 ก.ค. 2569</t>
+          <t>21 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>21 ก.ค. 2569</t>
+          <t>22 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>0768</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>22 ก.ค. 2569</t>
+          <t>23 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>0768</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>23 ก.ค. 2569</t>
+          <t>24 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>24 ก.ค. 2569</t>
+          <t>27 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>27 ก.ค. 2569</t>
+          <t>28 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>0480</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>28 ก.ค. 2569</t>
+          <t>29 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>0480</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6402,156 +6402,156 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>29 ก.ค. 2569</t>
+          <t>30 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>0702</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>30 ก.ค. 2569</t>
+          <t>31 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>0702</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>31 ก.ค. 2569</t>
+          <t>3 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>3 ส.ค. 2569</t>
+          <t>4 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>4 ส.ค. 2569</t>
+          <t>5 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5 ส.ค. 2569</t>
+          <t>6 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>6 ส.ค. 2569</t>
+          <t>7 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6563,506 +6563,484 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>7 ส.ค. 2569</t>
+          <t>10 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>10 ส.ค. 2569</t>
+          <t>11 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>11 ส.ค. 2569</t>
+          <t>12 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>12 ส.ค. 2569</t>
+          <t>13 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>13 ส.ค. 2569</t>
+          <t>14 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>14 ส.ค. 2569</t>
+          <t>17 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>17 ส.ค. 2569</t>
+          <t>18 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>18 ส.ค. 2569</t>
+          <t>19 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>19 ส.ค. 2569</t>
+          <t>20 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>20 ส.ค. 2569</t>
+          <t>21 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>0253</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>21 ส.ค. 2569</t>
+          <t>24 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>0253</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>24 ส.ค. 2569</t>
+          <t>25 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>25 ส.ค. 2569</t>
+          <t>26 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>26 ส.ค. 2569</t>
+          <t>27 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>27 ส.ค. 2569</t>
+          <t>28 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>0623</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>28 ส.ค. 2569</t>
+          <t>31 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>0623</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>31 ส.ค. 2569</t>
+          <t>1 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1 ก.ย. 2569</t>
+          <t>2 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2 ก.ย. 2569</t>
+          <t>4 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3 ก.ย. 2569</t>
+          <t>7 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>4 ก.ย. 2569</t>
+          <t>8 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>7 ก.ย. 2569</t>
+          <t>9 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>8 ก.ย. 2569</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>3743</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D301"/>
+  <dimension ref="A1:D304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5221,1178 +5221,1178 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>15 พ.ค. 2569</t>
+          <t>14 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>18 พ.ค. 2569</t>
+          <t>15 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>19 พ.ค. 2569</t>
+          <t>18 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>20 พ.ค. 2569</t>
+          <t>19 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>21 พ.ค. 2569</t>
+          <t>20 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>22 พ.ค. 2569</t>
+          <t>21 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>25 พ.ค. 2569</t>
+          <t>22 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>26 พ.ค. 2569</t>
+          <t>25 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>27 พ.ค. 2569</t>
+          <t>26 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>28 พ.ค. 2569</t>
+          <t>27 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>29 พ.ค. 2569</t>
+          <t>28 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1 มิ.ย. 2569</t>
+          <t>29 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2 มิ.ย. 2569</t>
+          <t>1 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3 มิ.ย. 2569</t>
+          <t>2 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>0549</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>4 มิ.ย. 2569</t>
+          <t>3 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>0549</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5 มิ.ย. 2569</t>
+          <t>4 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>8 มิ.ย. 2569</t>
+          <t>5 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>9 มิ.ย. 2569</t>
+          <t>8 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>10 มิ.ย. 2569</t>
+          <t>9 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>11 มิ.ย. 2569</t>
+          <t>10 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>12 มิ.ย. 2569</t>
+          <t>11 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>15 มิ.ย. 2569</t>
+          <t>12 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>16 มิ.ย. 2569</t>
+          <t>15 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>17 มิ.ย. 2569</t>
+          <t>16 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>18 มิ.ย. 2569</t>
+          <t>17 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>19 มิ.ย. 2569</t>
+          <t>18 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>22 มิ.ย. 2569</t>
+          <t>19 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>23 มิ.ย. 2569</t>
+          <t>22 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>24 มิ.ย. 2569</t>
+          <t>23 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>25 มิ.ย. 2569</t>
+          <t>24 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>26 มิ.ย. 2569</t>
+          <t>25 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>29 มิ.ย. 2569</t>
+          <t>26 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>30 มิ.ย. 2569</t>
+          <t>29 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1 ก.ค. 2569</t>
+          <t>30 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>83</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2 ก.ค. 2569</t>
+          <t>1 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3 ก.ค. 2569</t>
+          <t>2 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>6 ก.ค. 2569</t>
+          <t>3 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>7 ก.ค. 2569</t>
+          <t>6 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>8 ก.ค. 2569</t>
+          <t>7 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>9 ก.ค. 2569</t>
+          <t>8 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>10 ก.ค. 2569</t>
+          <t>9 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>13 ก.ค. 2569</t>
+          <t>10 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>14 ก.ค. 2569</t>
+          <t>13 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>15 ก.ค. 2569</t>
+          <t>14 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>16 ก.ค. 2569</t>
+          <t>15 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>93</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>17 ก.ค. 2569</t>
+          <t>16 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>20 ก.ค. 2569</t>
+          <t>17 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>21 ก.ค. 2569</t>
+          <t>20 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>22 ก.ค. 2569</t>
+          <t>21 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>0768</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>23 ก.ค. 2569</t>
+          <t>22 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>0768</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>24 ก.ค. 2569</t>
+          <t>23 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>27 ก.ค. 2569</t>
+          <t>24 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>28 ก.ค. 2569</t>
+          <t>27 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>0480</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>29 ก.ค. 2569</t>
+          <t>28 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>0480</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6402,156 +6402,156 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>30 ก.ค. 2569</t>
+          <t>29 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>0702</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>31 ก.ค. 2569</t>
+          <t>30 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>0702</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>3 ส.ค. 2569</t>
+          <t>31 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>4 ส.ค. 2569</t>
+          <t>3 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>5 ส.ค. 2569</t>
+          <t>4 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>6 ส.ค. 2569</t>
+          <t>5 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>7 ส.ค. 2569</t>
+          <t>6 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6563,484 +6563,550 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>10 ส.ค. 2569</t>
+          <t>7 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>11 ส.ค. 2569</t>
+          <t>10 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>12 ส.ค. 2569</t>
+          <t>11 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>13 ส.ค. 2569</t>
+          <t>12 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>14 ส.ค. 2569</t>
+          <t>13 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>17 ส.ค. 2569</t>
+          <t>14 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>18 ส.ค. 2569</t>
+          <t>17 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>19 ส.ค. 2569</t>
+          <t>18 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>20 ส.ค. 2569</t>
+          <t>19 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>21 ส.ค. 2569</t>
+          <t>20 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>0253</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>24 ส.ค. 2569</t>
+          <t>21 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>0253</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>25 ส.ค. 2569</t>
+          <t>24 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>26 ส.ค. 2569</t>
+          <t>25 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>27 ส.ค. 2569</t>
+          <t>26 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>28 ส.ค. 2569</t>
+          <t>27 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>0623</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>31 ส.ค. 2569</t>
+          <t>28 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>0623</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1 ก.ย. 2569</t>
+          <t>31 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2 ก.ย. 2569</t>
+          <t>1 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>4 ก.ย. 2569</t>
+          <t>2 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>7 ก.ย. 2569</t>
+          <t>3 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>8 ก.ย. 2569</t>
+          <t>4 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
+          <t>7 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>8 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>3743</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
           <t>9 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B303" t="inlineStr">
         <is>
           <t>3816</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
+      <c r="C303" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr">
+      <c r="D303" t="inlineStr">
         <is>
           <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>10 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>7128</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>71</t>
         </is>
       </c>
     </row>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -1107,2146 +1107,2146 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17 มี.ค. 2568</t>
+          <t>19 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>19 มี.ค. 2568</t>
+          <t>21 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>21 มี.ค. 2568</t>
+          <t>24 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>24 มี.ค. 2568</t>
+          <t>26 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>26 มี.ค. 2568</t>
+          <t>28 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>28 มี.ค. 2568</t>
+          <t>31 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>31 มี.ค. 2568</t>
+          <t>2 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>0609</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2 เม.ย. 2568</t>
+          <t>4 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0609</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4 เม.ย. 2568</t>
+          <t>7 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7 เม.ย. 2568</t>
+          <t>9 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9 เม.ย. 2568</t>
+          <t>11 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>11 เม.ย. 2568</t>
+          <t>18 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>18 เม.ย. 2568</t>
+          <t>21 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21 เม.ย. 2568</t>
+          <t>23 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>23 เม.ย. 2568</t>
+          <t>25 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25 เม.ย. 2568</t>
+          <t>28 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>0702</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28 เม.ย. 2568</t>
+          <t>30 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0702</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>30 เม.ย. 2568</t>
+          <t>2 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2 พ.ค. 2568</t>
+          <t>5 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5 พ.ค. 2568</t>
+          <t>7 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>0827</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7 พ.ค. 2568</t>
+          <t>9 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0827</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9 พ.ค. 2568</t>
+          <t>12 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>12 พ.ค. 2568</t>
+          <t>14 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>14 พ.ค. 2568</t>
+          <t>16 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16 พ.ค. 2568</t>
+          <t>19 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19 พ.ค. 2568</t>
+          <t>21 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>21 พ.ค. 2568</t>
+          <t>23 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>23 พ.ค. 2568</t>
+          <t>26 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>26 พ.ค. 2568</t>
+          <t>28 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>28 พ.ค. 2568</t>
+          <t>30 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>30 พ.ค. 2568</t>
+          <t>2 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2 มิ.ย. 2568</t>
+          <t>4 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4 มิ.ย. 2568</t>
+          <t>6 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6 มิ.ย. 2568</t>
+          <t>9 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>9 มิ.ย. 2568</t>
+          <t>11 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>11 มิ.ย. 2568</t>
+          <t>13 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>13 มิ.ย. 2568</t>
+          <t>16 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>16 มิ.ย. 2568</t>
+          <t>18 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>18 มิ.ย. 2568</t>
+          <t>20 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20 มิ.ย. 2568</t>
+          <t>23 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>23 มิ.ย. 2568</t>
+          <t>25 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>25 มิ.ย. 2568</t>
+          <t>27 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>27 มิ.ย. 2568</t>
+          <t>30 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>30 มิ.ย. 2568</t>
+          <t>2 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2 ก.ค. 2568</t>
+          <t>4 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4 ก.ค. 2568</t>
+          <t>7 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7 ก.ค. 2568</t>
+          <t>9 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9 ก.ค. 2568</t>
+          <t>11 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11 ก.ค. 2568</t>
+          <t>14 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>14 ก.ค. 2568</t>
+          <t>16 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>16 ก.ค. 2568</t>
+          <t>18 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>18 ก.ค. 2568</t>
+          <t>21 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>21 ก.ค. 2568</t>
+          <t>23 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>0440</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>23 ก.ค. 2568</t>
+          <t>25 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0440</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>25 ก.ค. 2568</t>
+          <t>28 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>28 ก.ค. 2568</t>
+          <t>30 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>30 ก.ค. 2568</t>
+          <t>1 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1 ส.ค. 2568</t>
+          <t>4 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4 ส.ค. 2568</t>
+          <t>6 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6 ส.ค. 2568</t>
+          <t>8 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8 ส.ค. 2568</t>
+          <t>11 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>11 ส.ค. 2568</t>
+          <t>13 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>13 ส.ค. 2568</t>
+          <t>15 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>15 ส.ค. 2568</t>
+          <t>18 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>18 ส.ค. 2568</t>
+          <t>20 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>0722</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20 ส.ค. 2568</t>
+          <t>22 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0722</t>
+          <t>0568</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>22 ส.ค. 2568</t>
+          <t>25 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0568</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>25 ส.ค. 2568</t>
+          <t>27 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>27 ส.ค. 2568</t>
+          <t>29 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>29 ส.ค. 2568</t>
+          <t>1 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1 ก.ย. 2568</t>
+          <t>3 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>0701</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3 ก.ย. 2568</t>
+          <t>5 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0701</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5 ก.ย. 2568</t>
+          <t>8 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8 ก.ย. 2568</t>
+          <t>10 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>10 ก.ย. 2568</t>
+          <t>12 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>0188</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>12 ก.ย. 2568</t>
+          <t>15 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0188</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>15 ก.ย. 2568</t>
+          <t>17 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>0543</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>17 ก.ย. 2568</t>
+          <t>19 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0543</t>
+          <t>0862</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>19 ก.ย. 2568</t>
+          <t>22 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0862</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>92</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>22 ก.ย. 2568</t>
+          <t>24 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>24 ก.ย. 2568</t>
+          <t>26 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>26 ก.ย. 2568</t>
+          <t>29 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>29 ก.ย. 2568</t>
+          <t>1 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1 ต.ค. 2568</t>
+          <t>3 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3 ต.ค. 2568</t>
+          <t>6 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>6 ต.ค. 2568</t>
+          <t>8 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>8 ต.ค. 2568</t>
+          <t>10 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10 ต.ค. 2568</t>
+          <t>13 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>13 ต.ค. 2568</t>
+          <t>15 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>15 ต.ค. 2568</t>
+          <t>17 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>17 ต.ค. 2568</t>
+          <t>20 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>20 ต.ค. 2568</t>
+          <t>22 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>22 ต.ค. 2568</t>
+          <t>24 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>24 ต.ค. 2568</t>
+          <t>27 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>27 ต.ค. 2568</t>
+          <t>29 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>29 ต.ค. 2568</t>
+          <t>31 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>31 ต.ค. 2568</t>
+          <t>3 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3 พ.ย. 2568</t>
+          <t>5 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3256,811 +3256,811 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5 พ.ย. 2568</t>
+          <t>7 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>7 พ.ย. 2568</t>
+          <t>10 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10 พ.ย. 2568</t>
+          <t>12 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>12 พ.ย. 2568</t>
+          <t>14 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>9877</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>14 พ.ย. 2568</t>
+          <t>17 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>17 พ.ย. 2568</t>
+          <t>19 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>19 พ.ย. 2568</t>
+          <t>21 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>21 พ.ย. 2568</t>
+          <t>24 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>24 พ.ย. 2568</t>
+          <t>26 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>26 พ.ย. 2568</t>
+          <t>28 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>28 พ.ย. 2568</t>
+          <t>1 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1 ธ.ค. 2568</t>
+          <t>3 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3 ธ.ค. 2568</t>
+          <t>5 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5 ธ.ค. 2568</t>
+          <t>8 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8 ธ.ค. 2568</t>
+          <t>10 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>10 ธ.ค. 2568</t>
+          <t>12 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>12 ธ.ค. 2568</t>
+          <t>15 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>15 ธ.ค. 2568</t>
+          <t>17 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>17 ธ.ค. 2568</t>
+          <t>19 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>19 ธ.ค. 2568</t>
+          <t>22 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>22 ธ.ค. 2568</t>
+          <t>24 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>24 ธ.ค. 2568</t>
+          <t>26 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>0052</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>00</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>26 ธ.ค. 2568</t>
+          <t>29 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0052</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>29 ธ.ค. 2568</t>
+          <t>31 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>31 ธ.ค. 2568</t>
+          <t>2 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2 ม.ค. 2569</t>
+          <t>5 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5 ม.ค. 2569</t>
+          <t>7 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>7 ม.ค. 2569</t>
+          <t>9 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>0905</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>9 ม.ค. 2569</t>
+          <t>12 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0905</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>12 ม.ค. 2569</t>
+          <t>14 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>14 ม.ค. 2569</t>
+          <t>16 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>16 ม.ค. 2569</t>
+          <t>19 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>19 ม.ค. 2569</t>
+          <t>21 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>21 ม.ค. 2569</t>
+          <t>23 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>23 ม.ค. 2569</t>
+          <t>26 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>0932</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>26 ม.ค. 2569</t>
+          <t>28 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0932</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>28 ม.ค. 2569</t>
+          <t>30 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4070,24 +4070,24 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>30 ม.ค. 2569</t>
+          <t>2 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4099,303 +4099,303 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2 ก.พ. 2569</t>
+          <t>4 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4 ก.พ. 2569</t>
+          <t>6 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6 ก.พ. 2569</t>
+          <t>9 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>9 ก.พ. 2569</t>
+          <t>11 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>11 ก.พ. 2569</t>
+          <t>13 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>13 ก.พ. 2569</t>
+          <t>16 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>16 ก.พ. 2569</t>
+          <t>18 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>18 ก.พ. 2569</t>
+          <t>20 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>20 ก.พ. 2569</t>
+          <t>23 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>00</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>23 ก.พ. 2569</t>
+          <t>25 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>25 ก.พ. 2569</t>
+          <t>27 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>27 ก.พ. 2569</t>
+          <t>2 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2 มี.ค. 2569</t>
+          <t>4 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>4 มี.ค. 2569</t>
+          <t>6 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4407,518 +4407,518 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>6 มี.ค. 2569</t>
+          <t>11 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>11 มี.ค. 2569</t>
+          <t>13 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>13 มี.ค. 2569</t>
+          <t>16 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>16 มี.ค. 2569</t>
+          <t>18 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>18 มี.ค. 2569</t>
+          <t>20 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>20 มี.ค. 2569</t>
+          <t>23 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>23 มี.ค. 2569</t>
+          <t>25 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>25 มี.ค. 2569</t>
+          <t>27 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>27 มี.ค. 2569</t>
+          <t>30 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>30 มี.ค. 2569</t>
+          <t>1 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1 เม.ย. 2569</t>
+          <t>2 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>0643</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2 เม.ย. 2569</t>
+          <t>3 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0643</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3 เม.ย. 2569</t>
+          <t>6 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>6 เม.ย. 2569</t>
+          <t>7 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>7 เม.ย. 2569</t>
+          <t>8 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>8 เม.ย. 2569</t>
+          <t>9 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>9 เม.ย. 2569</t>
+          <t>10 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>0389</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>10 เม.ย. 2569</t>
+          <t>13 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0389</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>13 เม.ย. 2569</t>
+          <t>17 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>17 เม.ย. 2569</t>
+          <t>20 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>0599</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>20 เม.ย. 2569</t>
+          <t>21 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0599</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>21 เม.ย. 2569</t>
+          <t>22 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>22 เม.ย. 2569</t>
+          <t>23 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>23 เม.ย. 2569</t>
+          <t>24 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4928,46 +4928,46 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>24 เม.ย. 2569</t>
+          <t>27 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>0927</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>27 เม.ย. 2569</t>
+          <t>28 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0927</t>
+          <t>0947</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4979,1420 +4979,1420 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>28 เม.ย. 2569</t>
+          <t>29 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0947</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>29 เม.ย. 2569</t>
+          <t>30 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>30 เม.ย. 2569</t>
+          <t>4 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4 พ.ค. 2569</t>
+          <t>5 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5 พ.ค. 2569</t>
+          <t>6 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>6 พ.ค. 2569</t>
+          <t>7 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>7 พ.ค. 2569</t>
+          <t>8 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>8 พ.ค. 2569</t>
+          <t>11 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>11 พ.ค. 2569</t>
+          <t>12 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>12 พ.ค. 2569</t>
+          <t>13 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>0572</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>13 พ.ค. 2569</t>
+          <t>14 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>0572</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>14 พ.ค. 2569</t>
+          <t>15 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>15 พ.ค. 2569</t>
+          <t>18 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>18 พ.ค. 2569</t>
+          <t>19 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>19 พ.ค. 2569</t>
+          <t>20 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>20 พ.ค. 2569</t>
+          <t>21 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>21 พ.ค. 2569</t>
+          <t>22 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>22 พ.ค. 2569</t>
+          <t>25 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>25 พ.ค. 2569</t>
+          <t>26 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>26 พ.ค. 2569</t>
+          <t>27 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>27 พ.ค. 2569</t>
+          <t>28 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>28 พ.ค. 2569</t>
+          <t>29 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>29 พ.ค. 2569</t>
+          <t>1 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1 มิ.ย. 2569</t>
+          <t>2 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2 มิ.ย. 2569</t>
+          <t>3 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>0549</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3 มิ.ย. 2569</t>
+          <t>4 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0549</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>4 มิ.ย. 2569</t>
+          <t>5 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5 มิ.ย. 2569</t>
+          <t>8 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>8 มิ.ย. 2569</t>
+          <t>9 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>9 มิ.ย. 2569</t>
+          <t>10 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>10 มิ.ย. 2569</t>
+          <t>11 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>11 มิ.ย. 2569</t>
+          <t>12 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>12 มิ.ย. 2569</t>
+          <t>15 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>15 มิ.ย. 2569</t>
+          <t>16 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>16 มิ.ย. 2569</t>
+          <t>17 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>17 มิ.ย. 2569</t>
+          <t>18 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>18 มิ.ย. 2569</t>
+          <t>19 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>19 มิ.ย. 2569</t>
+          <t>22 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>22 มิ.ย. 2569</t>
+          <t>23 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>23 มิ.ย. 2569</t>
+          <t>24 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>24 มิ.ย. 2569</t>
+          <t>25 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>25 มิ.ย. 2569</t>
+          <t>26 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>26 มิ.ย. 2569</t>
+          <t>29 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>29 มิ.ย. 2569</t>
+          <t>30 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>83</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>30 มิ.ย. 2569</t>
+          <t>1 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1 ก.ค. 2569</t>
+          <t>2 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2 ก.ค. 2569</t>
+          <t>3 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3 ก.ค. 2569</t>
+          <t>6 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>6 ก.ค. 2569</t>
+          <t>7 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>7 ก.ค. 2569</t>
+          <t>8 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>8 ก.ค. 2569</t>
+          <t>9 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>9 ก.ค. 2569</t>
+          <t>10 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>10 ก.ค. 2569</t>
+          <t>13 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>13 ก.ค. 2569</t>
+          <t>14 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>14 ก.ค. 2569</t>
+          <t>15 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>93</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>15 ก.ค. 2569</t>
+          <t>16 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>16 ก.ค. 2569</t>
+          <t>17 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>17 ก.ค. 2569</t>
+          <t>20 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>20 ก.ค. 2569</t>
+          <t>21 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>21 ก.ค. 2569</t>
+          <t>22 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>0768</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>22 ก.ค. 2569</t>
+          <t>23 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>0768</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>23 ก.ค. 2569</t>
+          <t>24 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>24 ก.ค. 2569</t>
+          <t>27 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>27 ก.ค. 2569</t>
+          <t>28 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>0480</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>28 ก.ค. 2569</t>
+          <t>29 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>0480</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6402,156 +6402,156 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>29 ก.ค. 2569</t>
+          <t>30 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>0702</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>30 ก.ค. 2569</t>
+          <t>31 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>0702</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>31 ก.ค. 2569</t>
+          <t>3 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>3 ส.ค. 2569</t>
+          <t>4 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>4 ส.ค. 2569</t>
+          <t>5 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5 ส.ค. 2569</t>
+          <t>6 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>6 ส.ค. 2569</t>
+          <t>7 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6563,550 +6563,550 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>7 ส.ค. 2569</t>
+          <t>10 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>10 ส.ค. 2569</t>
+          <t>11 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>11 ส.ค. 2569</t>
+          <t>12 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>12 ส.ค. 2569</t>
+          <t>13 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>13 ส.ค. 2569</t>
+          <t>14 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>14 ส.ค. 2569</t>
+          <t>17 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>17 ส.ค. 2569</t>
+          <t>18 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>18 ส.ค. 2569</t>
+          <t>19 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>19 ส.ค. 2569</t>
+          <t>20 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>20 ส.ค. 2569</t>
+          <t>21 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>0253</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>21 ส.ค. 2569</t>
+          <t>24 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>0253</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>24 ส.ค. 2569</t>
+          <t>25 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>25 ส.ค. 2569</t>
+          <t>26 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>26 ส.ค. 2569</t>
+          <t>27 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>27 ส.ค. 2569</t>
+          <t>28 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>0623</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>28 ส.ค. 2569</t>
+          <t>31 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>0623</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>31 ส.ค. 2569</t>
+          <t>1 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1 ก.ย. 2569</t>
+          <t>2 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2 ก.ย. 2569</t>
+          <t>3 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3 ก.ย. 2569</t>
+          <t>4 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>4 ก.ย. 2569</t>
+          <t>7 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>7 ก.ย. 2569</t>
+          <t>8 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>8 ก.ย. 2569</t>
+          <t>9 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>9 ก.ย. 2569</t>
+          <t>10 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>7128</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>71</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>10 ก.ย. 2569</t>
+          <t>11 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>33</t>
         </is>
       </c>
     </row>

--- a/lao_history.xlsx
+++ b/lao_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D304"/>
+  <dimension ref="A1:D305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1107,2146 +1107,2146 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>19 มี.ค. 2568</t>
+          <t>17 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>21 มี.ค. 2568</t>
+          <t>19 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>24 มี.ค. 2568</t>
+          <t>21 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>26 มี.ค. 2568</t>
+          <t>24 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>28 มี.ค. 2568</t>
+          <t>26 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>31 มี.ค. 2568</t>
+          <t>28 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2 เม.ย. 2568</t>
+          <t>31 มี.ค. 2568</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0609</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4 เม.ย. 2568</t>
+          <t>2 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>0609</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7 เม.ย. 2568</t>
+          <t>4 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9 เม.ย. 2568</t>
+          <t>7 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>11 เม.ย. 2568</t>
+          <t>9 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>18 เม.ย. 2568</t>
+          <t>11 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21 เม.ย. 2568</t>
+          <t>18 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>23 เม.ย. 2568</t>
+          <t>21 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25 เม.ย. 2568</t>
+          <t>23 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28 เม.ย. 2568</t>
+          <t>25 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0702</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>30 เม.ย. 2568</t>
+          <t>28 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>0702</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2 พ.ค. 2568</t>
+          <t>30 เม.ย. 2568</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5 พ.ค. 2568</t>
+          <t>2 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7 พ.ค. 2568</t>
+          <t>5 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0827</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>9 พ.ค. 2568</t>
+          <t>7 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>0827</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>12 พ.ค. 2568</t>
+          <t>9 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>14 พ.ค. 2568</t>
+          <t>12 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16 พ.ค. 2568</t>
+          <t>14 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19 พ.ค. 2568</t>
+          <t>16 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>21 พ.ค. 2568</t>
+          <t>19 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>23 พ.ค. 2568</t>
+          <t>21 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>26 พ.ค. 2568</t>
+          <t>23 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>28 พ.ค. 2568</t>
+          <t>26 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>30 พ.ค. 2568</t>
+          <t>28 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2 มิ.ย. 2568</t>
+          <t>30 พ.ค. 2568</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4 มิ.ย. 2568</t>
+          <t>2 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6 มิ.ย. 2568</t>
+          <t>4 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9 มิ.ย. 2568</t>
+          <t>6 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>11 มิ.ย. 2568</t>
+          <t>9 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>13 มิ.ย. 2568</t>
+          <t>11 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16 มิ.ย. 2568</t>
+          <t>13 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>18 มิ.ย. 2568</t>
+          <t>16 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20 มิ.ย. 2568</t>
+          <t>18 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>23 มิ.ย. 2568</t>
+          <t>20 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>25 มิ.ย. 2568</t>
+          <t>23 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>27 มิ.ย. 2568</t>
+          <t>25 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>30 มิ.ย. 2568</t>
+          <t>27 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2 ก.ค. 2568</t>
+          <t>30 มิ.ย. 2568</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4 ก.ค. 2568</t>
+          <t>2 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7 ก.ค. 2568</t>
+          <t>4 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9 ก.ค. 2568</t>
+          <t>7 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11 ก.ค. 2568</t>
+          <t>9 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>14 ก.ค. 2568</t>
+          <t>11 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>16 ก.ค. 2568</t>
+          <t>14 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>18 ก.ค. 2568</t>
+          <t>16 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>21 ก.ค. 2568</t>
+          <t>18 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>23 ก.ค. 2568</t>
+          <t>21 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0440</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>25 ก.ค. 2568</t>
+          <t>23 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>0440</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>28 ก.ค. 2568</t>
+          <t>25 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>30 ก.ค. 2568</t>
+          <t>28 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1 ส.ค. 2568</t>
+          <t>30 ก.ค. 2568</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4 ส.ค. 2568</t>
+          <t>1 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6 ส.ค. 2568</t>
+          <t>4 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8 ส.ค. 2568</t>
+          <t>6 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>11 ส.ค. 2568</t>
+          <t>8 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>13 ส.ค. 2568</t>
+          <t>11 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>15 ส.ค. 2568</t>
+          <t>13 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>18 ส.ค. 2568</t>
+          <t>15 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20 ส.ค. 2568</t>
+          <t>18 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0722</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>22 ส.ค. 2568</t>
+          <t>20 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0568</t>
+          <t>0722</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>25 ส.ค. 2568</t>
+          <t>22 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>0568</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>27 ส.ค. 2568</t>
+          <t>25 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>29 ส.ค. 2568</t>
+          <t>27 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1 ก.ย. 2568</t>
+          <t>29 ส.ค. 2568</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3 ก.ย. 2568</t>
+          <t>1 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0701</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5 ก.ย. 2568</t>
+          <t>3 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>0701</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8 ก.ย. 2568</t>
+          <t>5 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>10 ก.ย. 2568</t>
+          <t>8 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>12 ก.ย. 2568</t>
+          <t>10 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0188</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>15 ก.ย. 2568</t>
+          <t>12 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>0188</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>17 ก.ย. 2568</t>
+          <t>15 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0543</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>19 ก.ย. 2568</t>
+          <t>17 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0862</t>
+          <t>0543</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>22 ก.ย. 2568</t>
+          <t>19 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>0862</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>24 ก.ย. 2568</t>
+          <t>22 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>92</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>26 ก.ย. 2568</t>
+          <t>24 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>29 ก.ย. 2568</t>
+          <t>26 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1 ต.ค. 2568</t>
+          <t>29 ก.ย. 2568</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3 ต.ค. 2568</t>
+          <t>1 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>6 ต.ค. 2568</t>
+          <t>3 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>8 ต.ค. 2568</t>
+          <t>6 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10 ต.ค. 2568</t>
+          <t>8 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>13 ต.ค. 2568</t>
+          <t>10 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>15 ต.ค. 2568</t>
+          <t>13 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>17 ต.ค. 2568</t>
+          <t>15 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>20 ต.ค. 2568</t>
+          <t>17 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>22 ต.ค. 2568</t>
+          <t>20 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>24 ต.ค. 2568</t>
+          <t>22 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>27 ต.ค. 2568</t>
+          <t>24 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>29 ต.ค. 2568</t>
+          <t>27 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>31 ต.ค. 2568</t>
+          <t>29 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3 พ.ย. 2568</t>
+          <t>31 ต.ค. 2568</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5 พ.ย. 2568</t>
+          <t>3 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3256,811 +3256,811 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>7 พ.ย. 2568</t>
+          <t>5 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>10 พ.ย. 2568</t>
+          <t>7 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>12 พ.ย. 2568</t>
+          <t>10 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>14 พ.ย. 2568</t>
+          <t>12 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>17 พ.ย. 2568</t>
+          <t>14 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>9877</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>19 พ.ย. 2568</t>
+          <t>17 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>21 พ.ย. 2568</t>
+          <t>19 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>24 พ.ย. 2568</t>
+          <t>21 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>26 พ.ย. 2568</t>
+          <t>24 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>28 พ.ย. 2568</t>
+          <t>26 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1 ธ.ค. 2568</t>
+          <t>28 พ.ย. 2568</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3 ธ.ค. 2568</t>
+          <t>1 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5 ธ.ค. 2568</t>
+          <t>3 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8 ธ.ค. 2568</t>
+          <t>5 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>10 ธ.ค. 2568</t>
+          <t>8 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>12 ธ.ค. 2568</t>
+          <t>10 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>15 ธ.ค. 2568</t>
+          <t>12 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>17 ธ.ค. 2568</t>
+          <t>15 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>19 ธ.ค. 2568</t>
+          <t>17 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>22 ธ.ค. 2568</t>
+          <t>19 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>24 ธ.ค. 2568</t>
+          <t>22 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>26 ธ.ค. 2568</t>
+          <t>24 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0052</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>29 ธ.ค. 2568</t>
+          <t>26 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>0052</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>00</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>31 ธ.ค. 2568</t>
+          <t>29 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2 ม.ค. 2569</t>
+          <t>31 ธ.ค. 2568</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5 ม.ค. 2569</t>
+          <t>2 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>7 ม.ค. 2569</t>
+          <t>5 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>9 ม.ค. 2569</t>
+          <t>7 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0905</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>12 ม.ค. 2569</t>
+          <t>9 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>0905</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>14 ม.ค. 2569</t>
+          <t>12 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>16 ม.ค. 2569</t>
+          <t>14 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>19 ม.ค. 2569</t>
+          <t>16 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>21 ม.ค. 2569</t>
+          <t>19 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>23 ม.ค. 2569</t>
+          <t>21 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>26 ม.ค. 2569</t>
+          <t>23 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0932</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>28 ม.ค. 2569</t>
+          <t>26 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>0932</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>30 ม.ค. 2569</t>
+          <t>28 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4070,24 +4070,24 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2 ก.พ. 2569</t>
+          <t>30 ม.ค. 2569</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4099,303 +4099,303 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4 ก.พ. 2569</t>
+          <t>2 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>6 ก.พ. 2569</t>
+          <t>4 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>9 ก.พ. 2569</t>
+          <t>6 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>11 ก.พ. 2569</t>
+          <t>9 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>13 ก.พ. 2569</t>
+          <t>11 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>16 ก.พ. 2569</t>
+          <t>13 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>18 ก.พ. 2569</t>
+          <t>16 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>20 ก.พ. 2569</t>
+          <t>18 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>23 ก.พ. 2569</t>
+          <t>20 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>25 ก.พ. 2569</t>
+          <t>23 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>00</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>27 ก.พ. 2569</t>
+          <t>25 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2 มี.ค. 2569</t>
+          <t>27 ก.พ. 2569</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>4 มี.ค. 2569</t>
+          <t>2 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>6 มี.ค. 2569</t>
+          <t>4 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4407,518 +4407,518 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>11 มี.ค. 2569</t>
+          <t>6 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>13 มี.ค. 2569</t>
+          <t>11 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>16 มี.ค. 2569</t>
+          <t>13 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>18 มี.ค. 2569</t>
+          <t>16 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>20 มี.ค. 2569</t>
+          <t>18 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>23 มี.ค. 2569</t>
+          <t>20 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>25 มี.ค. 2569</t>
+          <t>23 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>27 มี.ค. 2569</t>
+          <t>25 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>30 มี.ค. 2569</t>
+          <t>27 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1 เม.ย. 2569</t>
+          <t>30 มี.ค. 2569</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2 เม.ย. 2569</t>
+          <t>1 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0643</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3 เม.ย. 2569</t>
+          <t>2 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>0643</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>6 เม.ย. 2569</t>
+          <t>3 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>7 เม.ย. 2569</t>
+          <t>6 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>8 เม.ย. 2569</t>
+          <t>7 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>9 เม.ย. 2569</t>
+          <t>8 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>10 เม.ย. 2569</t>
+          <t>9 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>0389</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>13 เม.ย. 2569</t>
+          <t>10 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>0389</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>17 เม.ย. 2569</t>
+          <t>13 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>20 เม.ย. 2569</t>
+          <t>17 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>0599</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>21 เม.ย. 2569</t>
+          <t>20 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>0599</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>22 เม.ย. 2569</t>
+          <t>21 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>23 เม.ย. 2569</t>
+          <t>22 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>24 เม.ย. 2569</t>
+          <t>23 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4928,46 +4928,46 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>27 เม.ย. 2569</t>
+          <t>24 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>0927</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>28 เม.ย. 2569</t>
+          <t>27 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0947</t>
+          <t>0927</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4979,1420 +4979,1420 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>29 เม.ย. 2569</t>
+          <t>28 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>0947</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>30 เม.ย. 2569</t>
+          <t>29 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4 พ.ค. 2569</t>
+          <t>30 เม.ย. 2569</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>5 พ.ค. 2569</t>
+          <t>4 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>6 พ.ค. 2569</t>
+          <t>5 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>7 พ.ค. 2569</t>
+          <t>6 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8 พ.ค. 2569</t>
+          <t>7 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>11 พ.ค. 2569</t>
+          <t>8 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>12 พ.ค. 2569</t>
+          <t>11 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>13 พ.ค. 2569</t>
+          <t>12 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0572</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>14 พ.ค. 2569</t>
+          <t>13 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>0572</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>15 พ.ค. 2569</t>
+          <t>14 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>18 พ.ค. 2569</t>
+          <t>15 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>19 พ.ค. 2569</t>
+          <t>18 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>20 พ.ค. 2569</t>
+          <t>19 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>21 พ.ค. 2569</t>
+          <t>20 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>22 พ.ค. 2569</t>
+          <t>21 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>25 พ.ค. 2569</t>
+          <t>22 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>26 พ.ค. 2569</t>
+          <t>25 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>27 พ.ค. 2569</t>
+          <t>26 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>28 พ.ค. 2569</t>
+          <t>27 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>29 พ.ค. 2569</t>
+          <t>28 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1 มิ.ย. 2569</t>
+          <t>29 พ.ค. 2569</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2 มิ.ย. 2569</t>
+          <t>1 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3 มิ.ย. 2569</t>
+          <t>2 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>0549</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>4 มิ.ย. 2569</t>
+          <t>3 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>0549</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5 มิ.ย. 2569</t>
+          <t>4 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>8 มิ.ย. 2569</t>
+          <t>5 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>9 มิ.ย. 2569</t>
+          <t>8 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>10 มิ.ย. 2569</t>
+          <t>9 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>11 มิ.ย. 2569</t>
+          <t>10 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>12 มิ.ย. 2569</t>
+          <t>11 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>15 มิ.ย. 2569</t>
+          <t>12 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>16 มิ.ย. 2569</t>
+          <t>15 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>17 มิ.ย. 2569</t>
+          <t>16 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>18 มิ.ย. 2569</t>
+          <t>17 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>19 มิ.ย. 2569</t>
+          <t>18 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>22 มิ.ย. 2569</t>
+          <t>19 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>23 มิ.ย. 2569</t>
+          <t>22 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>24 มิ.ย. 2569</t>
+          <t>23 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>25 มิ.ย. 2569</t>
+          <t>24 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>26 มิ.ย. 2569</t>
+          <t>25 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>29 มิ.ย. 2569</t>
+          <t>26 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>30 มิ.ย. 2569</t>
+          <t>29 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1 ก.ค. 2569</t>
+          <t>30 มิ.ย. 2569</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>83</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2 ก.ค. 2569</t>
+          <t>1 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3 ก.ค. 2569</t>
+          <t>2 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>6 ก.ค. 2569</t>
+          <t>3 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>7 ก.ค. 2569</t>
+          <t>6 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>8 ก.ค. 2569</t>
+          <t>7 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>9 ก.ค. 2569</t>
+          <t>8 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>10 ก.ค. 2569</t>
+          <t>9 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>13 ก.ค. 2569</t>
+          <t>10 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>14 ก.ค. 2569</t>
+          <t>13 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>15 ก.ค. 2569</t>
+          <t>14 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>16 ก.ค. 2569</t>
+          <t>15 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>93</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>17 ก.ค. 2569</t>
+          <t>16 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>20 ก.ค. 2569</t>
+          <t>17 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>21 ก.ค. 2569</t>
+          <t>20 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>22 ก.ค. 2569</t>
+          <t>21 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>0768</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>23 ก.ค. 2569</t>
+          <t>22 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>0768</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>24 ก.ค. 2569</t>
+          <t>23 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>27 ก.ค. 2569</t>
+          <t>24 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>28 ก.ค. 2569</t>
+          <t>27 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>0480</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>29 ก.ค. 2569</t>
+          <t>28 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>0480</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6402,156 +6402,156 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>30 ก.ค. 2569</t>
+          <t>29 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>0702</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>31 ก.ค. 2569</t>
+          <t>30 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>0702</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>3 ส.ค. 2569</t>
+          <t>31 ก.ค. 2569</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>4 ส.ค. 2569</t>
+          <t>3 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>5 ส.ค. 2569</t>
+          <t>4 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>6 ส.ค. 2569</t>
+          <t>5 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>7 ส.ค. 2569</t>
+          <t>6 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6563,548 +6563,570 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>10 ส.ค. 2569</t>
+          <t>7 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>11 ส.ค. 2569</t>
+          <t>10 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>12 ส.ค. 2569</t>
+          <t>11 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>13 ส.ค. 2569</t>
+          <t>12 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>14 ส.ค. 2569</t>
+          <t>13 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>17 ส.ค. 2569</t>
+          <t>14 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>18 ส.ค. 2569</t>
+          <t>17 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>19 ส.ค. 2569</t>
+          <t>18 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>20 ส.ค. 2569</t>
+          <t>19 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>21 ส.ค. 2569</t>
+          <t>20 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>0253</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>24 ส.ค. 2569</t>
+          <t>21 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>0253</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>25 ส.ค. 2569</t>
+          <t>24 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>26 ส.ค. 2569</t>
+          <t>25 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>27 ส.ค. 2569</t>
+          <t>26 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>28 ส.ค. 2569</t>
+          <t>27 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>0623</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>31 ส.ค. 2569</t>
+          <t>28 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>0623</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1 ก.ย. 2569</t>
+          <t>31 ส.ค. 2569</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2 ก.ย. 2569</t>
+          <t>1 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3 ก.ย. 2569</t>
+          <t>2 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>4 ก.ย. 2569</t>
+          <t>3 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>7 ก.ย. 2569</t>
+          <t>4 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>8 ก.ย. 2569</t>
+          <t>7 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>9 ก.ย. 2569</t>
+          <t>8 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>10 ก.ย. 2569</t>
+          <t>9 ก.ย. 2569</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
+          <t>10 ก.ย. 2569</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>7128</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
           <t>11 ก.ย. 2569</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>3350</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr">
+      <c r="C305" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr">
+      <c r="D305" t="inlineStr">
         <is>
           <t>33</t>
         </is>
